--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2021_metropolitana.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2021_metropolitana.xlsx
@@ -195,7 +195,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 13:44</t>
+    <t xml:space="preserve">2026-09-09 20:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2021_metropolitana.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2021_metropolitana.xlsx
@@ -195,7 +195,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:06</t>
+    <t xml:space="preserve">2026-09-18 17:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2021_metropolitana.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2021_metropolitana.xlsx
@@ -30,162 +30,162 @@
     <t xml:space="preserve">Cobertura</t>
   </si>
   <si>
+    <t xml:space="preserve">Santiago</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calera de Tango</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alhué</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Miguel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Ramón</t>
+  </si>
+  <si>
+    <t xml:space="preserve">María Pinto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Granja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Joaquín</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cerro Navia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pirque</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melipilla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lo Espejo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pedro Aguirre Cerda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Cisterna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Padre Hurtado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El Bosque</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curacaví</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San José de Maipo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conchalí</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quinta Normal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Pintana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El Monte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lo Prado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Macul</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cerrillos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Florida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Renca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peñaflor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talagante</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isla de Maipo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Reina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peñalolén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Providencia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Bernardo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recoleta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Huechuraba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maipú</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pudahuel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puente Alto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ñuñoa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lampa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Las Condes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estación Central</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vitacura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Pedro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Independencia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quilicura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lo Barnechea</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tiltil</t>
   </si>
   <si>
-    <t xml:space="preserve">Lo Barnechea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quilicura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Independencia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Pedro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vitacura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estación Central</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Colina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Las Condes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lampa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ñuñoa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puente Alto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pudahuel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maipú</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Huechuraba</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recoleta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Bernardo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Providencia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peñalolén</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Reina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isla de Maipo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Talagante</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peñaflor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Renca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Florida</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cerrillos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Macul</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lo Prado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El Monte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Pintana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quinta Normal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conchalí</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San José de Maipo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curacaví</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El Bosque</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Padre Hurtado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Cisterna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pedro Aguirre Cerda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lo Espejo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melipilla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pirque</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cerro Navia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Joaquín</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Granja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">María Pinto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Ramón</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Miguel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alhué</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calera de Tango</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Santiago</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -195,7 +195,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 17:05</t>
+    <t xml:space="preserve">2026-09-27 21:49</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -615,13 +615,13 @@
         <v>4</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>10318</v>
+        <v>606793</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>21783</v>
+        <v>517280</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>47.37</v>
+        <v>117.3</v>
       </c>
     </row>
     <row r="3">
@@ -629,13 +629,13 @@
         <v>5</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>100026</v>
+        <v>31279</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>126816</v>
+        <v>29019</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>78.87</v>
+        <v>107.79</v>
       </c>
     </row>
     <row r="4">
@@ -643,13 +643,13 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>207568</v>
+        <v>7943</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>261993</v>
+        <v>7536</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>79.23</v>
+        <v>105.4</v>
       </c>
     </row>
     <row r="5">
@@ -657,13 +657,13 @@
         <v>7</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>117668</v>
+        <v>138864</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>147655</v>
+        <v>136835</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>79.69</v>
+        <v>101.48</v>
       </c>
     </row>
     <row r="6">
@@ -671,13 +671,13 @@
         <v>8</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>9738</v>
+        <v>87155</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>12132</v>
+        <v>86017</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>80.27</v>
+        <v>101.32</v>
       </c>
     </row>
     <row r="7">
@@ -685,13 +685,13 @@
         <v>9</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>78812</v>
+        <v>15201</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>97695</v>
+        <v>15132</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>80.67</v>
+        <v>100.46</v>
       </c>
     </row>
     <row r="8">
@@ -699,13 +699,13 @@
         <v>10</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>173857</v>
+        <v>119869</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>214470</v>
+        <v>122028</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>81.06</v>
+        <v>98.23</v>
       </c>
     </row>
     <row r="9">
@@ -713,13 +713,13 @@
         <v>11</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>151824</v>
+        <v>101813</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>185599</v>
+        <v>103871</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>81.8</v>
+        <v>98.02</v>
       </c>
     </row>
     <row r="10">
@@ -727,13 +727,13 @@
         <v>12</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>282651</v>
+        <v>139108</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>335296</v>
+        <v>142304</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>84.3</v>
+        <v>97.75</v>
       </c>
     </row>
     <row r="11">
@@ -741,13 +741,13 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>111471</v>
+        <v>30397</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>131436</v>
+        <v>31134</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>84.81</v>
+        <v>97.63</v>
       </c>
     </row>
     <row r="12">
@@ -755,13 +755,13 @@
         <v>14</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>218986</v>
+        <v>140100</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>255823</v>
+        <v>143779</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>85.6</v>
+        <v>97.44</v>
       </c>
     </row>
     <row r="13">
@@ -769,13 +769,13 @@
         <v>15</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>560990</v>
+        <v>108875</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>655033</v>
+        <v>111934</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>85.64</v>
+        <v>97.27</v>
       </c>
     </row>
     <row r="14">
@@ -783,13 +783,13 @@
         <v>16</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>221438</v>
+        <v>100496</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>256607</v>
+        <v>103381</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>86.29</v>
+        <v>97.21</v>
       </c>
     </row>
     <row r="15">
@@ -797,13 +797,13 @@
         <v>17</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>505122</v>
+        <v>104267</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>584053</v>
+        <v>107409</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>86.49</v>
+        <v>97.07</v>
       </c>
     </row>
     <row r="16">
@@ -811,13 +811,13 @@
         <v>18</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>99895</v>
+        <v>97794</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>114453</v>
+        <v>101126</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>87.28</v>
+        <v>96.71</v>
       </c>
     </row>
     <row r="17">
@@ -825,13 +825,13 @@
         <v>19</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>74124</v>
+        <v>72993</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>84379</v>
+        <v>76219</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>87.85</v>
+        <v>95.77</v>
       </c>
     </row>
     <row r="18">
@@ -839,13 +839,13 @@
         <v>20</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>170387</v>
+        <v>162282</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>193605</v>
+        <v>171789</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>88.01</v>
+        <v>94.47</v>
       </c>
     </row>
     <row r="19">
@@ -853,13 +853,13 @@
         <v>21</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>298785</v>
+        <v>34881</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>339043</v>
+        <v>36991</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>88.13</v>
+        <v>94.3</v>
       </c>
     </row>
     <row r="20">
@@ -867,13 +867,13 @@
         <v>22</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>142081</v>
+        <v>17822</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>160043</v>
+        <v>18917</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>88.78</v>
+        <v>94.21</v>
       </c>
     </row>
     <row r="21">
@@ -881,13 +881,13 @@
         <v>23</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>239380</v>
+        <v>130953</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>269296</v>
+        <v>139394</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>88.89</v>
+        <v>93.94</v>
       </c>
     </row>
     <row r="22">
@@ -895,13 +895,13 @@
         <v>24</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>90165</v>
+        <v>130150</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>100459</v>
+        <v>138904</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>89.75</v>
+        <v>93.7</v>
       </c>
     </row>
     <row r="23">
@@ -909,13 +909,13 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>36723</v>
+        <v>177428</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>40803</v>
+        <v>189454</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>90</v>
+        <v>93.65</v>
       </c>
     </row>
     <row r="24">
@@ -923,13 +923,13 @@
         <v>26</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>75068</v>
+        <v>38019</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>82900</v>
+        <v>40620</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>90.55</v>
+        <v>93.6</v>
       </c>
     </row>
     <row r="25">
@@ -937,13 +937,13 @@
         <v>27</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>93237</v>
+        <v>97397</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>102667</v>
+        <v>104405</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>90.81</v>
+        <v>93.29</v>
       </c>
     </row>
     <row r="26">
@@ -951,13 +951,13 @@
         <v>28</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>147773</v>
+        <v>125631</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>161959</v>
+        <v>136278</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>91.24</v>
+        <v>92.19</v>
       </c>
     </row>
     <row r="27">
@@ -965,13 +965,13 @@
         <v>29</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>370334</v>
+        <v>81892</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>405185</v>
+        <v>89520</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>91.4</v>
+        <v>91.48</v>
       </c>
     </row>
     <row r="28">
@@ -979,13 +979,13 @@
         <v>30</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>81892</v>
+        <v>370334</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>89520</v>
+        <v>405185</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>91.48</v>
+        <v>91.4</v>
       </c>
     </row>
     <row r="29">
@@ -993,13 +993,13 @@
         <v>31</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>125631</v>
+        <v>147773</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>136278</v>
+        <v>161959</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>92.19</v>
+        <v>91.24</v>
       </c>
     </row>
     <row r="30">
@@ -1007,13 +1007,13 @@
         <v>32</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>97397</v>
+        <v>93237</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>104405</v>
+        <v>102667</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>93.29</v>
+        <v>90.81</v>
       </c>
     </row>
     <row r="31">
@@ -1021,13 +1021,13 @@
         <v>33</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>38019</v>
+        <v>75068</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>40620</v>
+        <v>82900</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>93.6</v>
+        <v>90.55</v>
       </c>
     </row>
     <row r="32">
@@ -1035,13 +1035,13 @@
         <v>34</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>177428</v>
+        <v>36723</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>189454</v>
+        <v>40803</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>93.65</v>
+        <v>90</v>
       </c>
     </row>
     <row r="33">
@@ -1049,13 +1049,13 @@
         <v>35</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>130150</v>
+        <v>90165</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>138904</v>
+        <v>100459</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>93.7</v>
+        <v>89.75</v>
       </c>
     </row>
     <row r="34">
@@ -1063,13 +1063,13 @@
         <v>36</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>130953</v>
+        <v>239380</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>139394</v>
+        <v>269296</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>93.94</v>
+        <v>88.89</v>
       </c>
     </row>
     <row r="35">
@@ -1077,13 +1077,13 @@
         <v>37</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>17822</v>
+        <v>142081</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>18917</v>
+        <v>160043</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>94.21</v>
+        <v>88.78</v>
       </c>
     </row>
     <row r="36">
@@ -1091,13 +1091,13 @@
         <v>38</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>34881</v>
+        <v>298785</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>36991</v>
+        <v>339043</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>94.3</v>
+        <v>88.13</v>
       </c>
     </row>
     <row r="37">
@@ -1105,13 +1105,13 @@
         <v>39</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>162282</v>
+        <v>170387</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>171789</v>
+        <v>193605</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>94.47</v>
+        <v>88.01</v>
       </c>
     </row>
     <row r="38">
@@ -1119,13 +1119,13 @@
         <v>40</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>72993</v>
+        <v>74124</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>76219</v>
+        <v>84379</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>95.77</v>
+        <v>87.85</v>
       </c>
     </row>
     <row r="39">
@@ -1133,13 +1133,13 @@
         <v>41</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>97794</v>
+        <v>99895</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>101126</v>
+        <v>114453</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>96.71</v>
+        <v>87.28</v>
       </c>
     </row>
     <row r="40">
@@ -1147,13 +1147,13 @@
         <v>42</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>104267</v>
+        <v>505122</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>107409</v>
+        <v>584053</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>97.07</v>
+        <v>86.49</v>
       </c>
     </row>
     <row r="41">
@@ -1161,13 +1161,13 @@
         <v>43</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>100496</v>
+        <v>221438</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>103381</v>
+        <v>256607</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>97.21</v>
+        <v>86.29</v>
       </c>
     </row>
     <row r="42">
@@ -1175,13 +1175,13 @@
         <v>44</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>108875</v>
+        <v>560990</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>111934</v>
+        <v>655033</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>97.27</v>
+        <v>85.64</v>
       </c>
     </row>
     <row r="43">
@@ -1189,13 +1189,13 @@
         <v>45</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>140100</v>
+        <v>218986</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>143779</v>
+        <v>255823</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>97.44</v>
+        <v>85.6</v>
       </c>
     </row>
     <row r="44">
@@ -1203,13 +1203,13 @@
         <v>46</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>30397</v>
+        <v>111471</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>31134</v>
+        <v>131436</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>97.63</v>
+        <v>84.81</v>
       </c>
     </row>
     <row r="45">
@@ -1217,13 +1217,13 @@
         <v>47</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>139108</v>
+        <v>282651</v>
       </c>
       <c r="C45" s="2" t="n">
-        <v>142304</v>
+        <v>335296</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>97.75</v>
+        <v>84.3</v>
       </c>
     </row>
     <row r="46">
@@ -1231,13 +1231,13 @@
         <v>48</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>101813</v>
+        <v>151824</v>
       </c>
       <c r="C46" s="2" t="n">
-        <v>103871</v>
+        <v>185599</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>98.02</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="47">
@@ -1245,13 +1245,13 @@
         <v>49</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>119869</v>
+        <v>173857</v>
       </c>
       <c r="C47" s="2" t="n">
-        <v>122028</v>
+        <v>214470</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>98.23</v>
+        <v>81.06</v>
       </c>
     </row>
     <row r="48">
@@ -1259,13 +1259,13 @@
         <v>50</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>15201</v>
+        <v>78812</v>
       </c>
       <c r="C48" s="2" t="n">
-        <v>15132</v>
+        <v>97695</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>100.46</v>
+        <v>80.67</v>
       </c>
     </row>
     <row r="49">
@@ -1273,13 +1273,13 @@
         <v>51</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>87155</v>
+        <v>9738</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>86017</v>
+        <v>12132</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>101.32</v>
+        <v>80.27</v>
       </c>
     </row>
     <row r="50">
@@ -1287,13 +1287,13 @@
         <v>52</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>138864</v>
+        <v>117668</v>
       </c>
       <c r="C50" s="2" t="n">
-        <v>136835</v>
+        <v>147655</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>101.48</v>
+        <v>79.69</v>
       </c>
     </row>
     <row r="51">
@@ -1301,13 +1301,13 @@
         <v>53</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>7943</v>
+        <v>207568</v>
       </c>
       <c r="C51" s="2" t="n">
-        <v>7536</v>
+        <v>261993</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>105.4</v>
+        <v>79.23</v>
       </c>
     </row>
     <row r="52">
@@ -1315,13 +1315,13 @@
         <v>54</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>31279</v>
+        <v>100026</v>
       </c>
       <c r="C52" s="2" t="n">
-        <v>29019</v>
+        <v>126816</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>107.79</v>
+        <v>78.87</v>
       </c>
     </row>
     <row r="53">
@@ -1329,13 +1329,13 @@
         <v>55</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>606793</v>
+        <v>10318</v>
       </c>
       <c r="C53" s="2" t="n">
-        <v>517280</v>
+        <v>21783</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>117.3</v>
+        <v>47.37</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2021_metropolitana.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2021_metropolitana.xlsx
@@ -195,7 +195,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 21:49</t>
+    <t xml:space="preserve">2026-10-05 05:46</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
